--- a/samples/示例登分表_中考.xlsx
+++ b/samples/示例登分表_中考.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>赵俊杰</t>
+          <t>赵北辰</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>罗一桐</t>
+          <t>罗疏乔</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>黄欣轩</t>
+          <t>黄墨禾</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>杨梓桐</t>
+          <t>杨青乔</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>刘俊怡</t>
+          <t>刘北言</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>吴欣怡</t>
+          <t>吴墨言</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>郭梓远</t>
+          <t>郭青野</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>马俊怡</t>
+          <t>马北言</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>陈俊桐</t>
+          <t>陈北乔</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>徐明涵</t>
+          <t>徐和秋</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>高浩琪</t>
+          <t>高书澜</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>吴俊远</t>
+          <t>吴北野</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>赵浩桐</t>
+          <t>赵书乔</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>周雨杰</t>
+          <t>周南辰</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>罗雨轩</t>
+          <t>罗南舟</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杨佳宇</t>
+          <t>杨听白</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>徐明轩</t>
+          <t>徐和禾</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>马一轩</t>
+          <t>马疏舟</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>李欣杰</t>
+          <t>李墨辰</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>赵浩桐</t>
+          <t>赵书乔</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>黄子轩</t>
+          <t>黄砚舟</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杨欣桐</t>
+          <t>杨墨乔</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>马浩轩</t>
+          <t>马书禾</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>高佳涵</t>
+          <t>高听秋</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>罗思远</t>
+          <t>罗星野</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>杨子轩</t>
+          <t>杨砚禾</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>杨浩桐</t>
+          <t>杨书乔</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>杨子桐</t>
+          <t>杨砚乔</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>刘思宇</t>
+          <t>刘星白</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>李明涵</t>
+          <t>李和秋</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>杨欣涵</t>
+          <t>杨墨秋</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>杨俊琪</t>
+          <t>杨北澜</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>李一远</t>
+          <t>李疏野</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>郭明宇</t>
+          <t>郭和白</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>马梓远</t>
+          <t>马青野</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>陈浩桐</t>
+          <t>陈书乔</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>孙一涵</t>
+          <t>孙疏秋</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>朱雨宇</t>
+          <t>朱南白</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>刘雨杰</t>
+          <t>刘南辰</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>黄俊杰</t>
+          <t>黄北辰</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>罗欣远</t>
+          <t>罗墨野</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>胡一涵</t>
+          <t>胡疏秋</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>黄浩远</t>
+          <t>黄书野</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>刘俊诺</t>
+          <t>刘北桐</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>杨欣杰</t>
+          <t>杨墨辰</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>张明宇</t>
+          <t>张和白</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>郭欣轩</t>
+          <t>郭墨禾</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>罗思轩</t>
+          <t>罗星禾</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>马俊远</t>
+          <t>马北野</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>孙欣诺</t>
+          <t>孙墨桐</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>杨明怡</t>
+          <t>杨和言</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>何子涵</t>
+          <t>何砚秋</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>吴一远</t>
+          <t>吴疏野</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>孙雨琪</t>
+          <t>孙南澜</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>孙佳琪</t>
+          <t>孙听澜</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>周思琪</t>
+          <t>周星澜</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>林明杰</t>
+          <t>林和辰</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>黄欣远</t>
+          <t>黄墨野</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>王一杰</t>
+          <t>王疏辰</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>吴明琪</t>
+          <t>吴和澜</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>林欣琪</t>
+          <t>林墨澜</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>王欣涵</t>
+          <t>王墨秋</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>孙子琪</t>
+          <t>孙砚澜</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>郭佳涵</t>
+          <t>郭听秋</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>李梓桐</t>
+          <t>李青乔</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>吴雨琪</t>
+          <t>吴南澜</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>胡佳诺</t>
+          <t>胡听桐</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>刘一涵</t>
+          <t>刘疏秋</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>马明杰</t>
+          <t>马和辰</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>吴雨宇</t>
+          <t>吴南白</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>张一诺</t>
+          <t>张疏桐</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>朱俊琪</t>
+          <t>朱北澜</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>徐明宇</t>
+          <t>徐和白</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>周欣诺</t>
+          <t>周墨桐</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>周子怡</t>
+          <t>周砚言</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>何子宇</t>
+          <t>何砚白</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>赵浩涵</t>
+          <t>赵书秋</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>林梓桐</t>
+          <t>林青乔</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>郭俊怡</t>
+          <t>郭北言</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>杨思轩</t>
+          <t>杨星禾</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>郭浩涵</t>
+          <t>郭书秋</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>李浩杰</t>
+          <t>李书辰</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>孙欣远</t>
+          <t>孙墨野</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>王一涵</t>
+          <t>王疏秋</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>黄子诺</t>
+          <t>黄砚桐</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>王佳轩</t>
+          <t>王听禾</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>张明远</t>
+          <t>张和野</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>孙一涵</t>
+          <t>孙疏秋</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>周一琪</t>
+          <t>周疏澜</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>胡俊诺</t>
+          <t>胡北桐</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>孙明杰</t>
+          <t>孙和辰</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>罗欣宇</t>
+          <t>罗墨白</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>周浩诺</t>
+          <t>周书桐</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>张浩远</t>
+          <t>张书野</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>林浩涵</t>
+          <t>林书秋</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>黄雨桐</t>
+          <t>黄南乔</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>刘子轩</t>
+          <t>刘砚禾</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>罗思诺</t>
+          <t>罗星桐</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>陈欣怡</t>
+          <t>陈墨言</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>罗子轩</t>
+          <t>罗砚舟</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>郭雨轩</t>
+          <t>郭南舟</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>徐思诺</t>
+          <t>徐星桐</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>胡雨远</t>
+          <t>胡南野</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>马佳怡</t>
+          <t>马听言</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>杨雨涵</t>
+          <t>杨南秋</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>马一杰</t>
+          <t>马疏辰</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>郭佳怡</t>
+          <t>郭听言</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>高浩远</t>
+          <t>高书野</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>吴思桐</t>
+          <t>吴星乔</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>罗子怡</t>
+          <t>罗砚言</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>徐思琪</t>
+          <t>徐星澜</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>杨明怡</t>
+          <t>杨和言</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>林明宇</t>
+          <t>林和白</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>黄明轩</t>
+          <t>黄和禾</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>周佳宇</t>
+          <t>周听白</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>黄佳怡</t>
+          <t>黄听言</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>张佳轩</t>
+          <t>张听舟</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>刘子诺</t>
+          <t>刘砚桐</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>吴佳涵</t>
+          <t>吴听秋</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>马俊远</t>
+          <t>马北野</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>胡梓琪</t>
+          <t>胡青澜</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>吴浩轩</t>
+          <t>吴书舟</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>陈一琪</t>
+          <t>陈疏澜</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>罗一怡</t>
+          <t>罗疏言</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>杨思怡</t>
+          <t>杨星言</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>罗明琪</t>
+          <t>罗和澜</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>林浩轩</t>
+          <t>林书舟</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>罗浩宇</t>
+          <t>罗书白</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>朱明琪</t>
+          <t>朱和澜</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>高梓涵</t>
+          <t>高青秋</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>高思诺</t>
+          <t>高星桐</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>陈俊远</t>
+          <t>陈北野</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>罗雨远</t>
+          <t>罗南野</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>朱子宇</t>
+          <t>朱砚白</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>胡思杰</t>
+          <t>胡星辰</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>马欣怡</t>
+          <t>马墨言</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>罗佳杰</t>
+          <t>罗听辰</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>朱梓轩</t>
+          <t>朱青舟</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>刘俊轩</t>
+          <t>刘北禾</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>何浩怡</t>
+          <t>何书言</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>孙一涵</t>
+          <t>孙疏秋</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>徐梓杰</t>
+          <t>徐青辰</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>何思琪</t>
+          <t>何星澜</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>赵浩桐</t>
+          <t>赵书乔</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>罗浩杰</t>
+          <t>罗书辰</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>何子琪</t>
+          <t>何砚澜</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>吴欣桐</t>
+          <t>吴墨乔</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>胡明怡</t>
+          <t>胡和言</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>杨梓怡</t>
+          <t>杨青言</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>胡思杰</t>
+          <t>胡星辰</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>罗子怡</t>
+          <t>罗砚言</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>罗梓杰</t>
+          <t>罗青辰</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>罗浩诺</t>
+          <t>罗书桐</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>何梓桐</t>
+          <t>何青乔</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>朱浩诺</t>
+          <t>朱书桐</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>杨佳远</t>
+          <t>杨听野</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>李一桐</t>
+          <t>李疏乔</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>何欣轩</t>
+          <t>何墨舟</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>李子宇</t>
+          <t>李砚白</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>朱一涵</t>
+          <t>朱疏秋</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>刘佳远</t>
+          <t>刘听野</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>何欣杰</t>
+          <t>何墨辰</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>朱梓宇</t>
+          <t>朱青白</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>周欣远</t>
+          <t>周墨野</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>徐子怡</t>
+          <t>徐砚言</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>林俊涵</t>
+          <t>林北秋</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>徐明诺</t>
+          <t>徐和桐</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>赵雨诺</t>
+          <t>赵南桐</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>刘俊宇</t>
+          <t>刘北白</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>高明诺</t>
+          <t>高和桐</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>刘雨远</t>
+          <t>刘南野</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>陈浩涵</t>
+          <t>陈书秋</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>赵俊轩</t>
+          <t>赵北禾</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>林一桐</t>
+          <t>林疏乔</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>刘梓宇</t>
+          <t>刘青白</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>陈思远</t>
+          <t>陈星野</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>王梓宇</t>
+          <t>王青白</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>杨浩轩</t>
+          <t>杨书舟</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>高浩涵</t>
+          <t>高书秋</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>杨欣诺</t>
+          <t>杨墨桐</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>赵佳桐</t>
+          <t>赵听乔</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>郭佳桐</t>
+          <t>郭听乔</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>郭子杰</t>
+          <t>郭砚辰</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>罗佳怡</t>
+          <t>罗听言</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>黄梓远</t>
+          <t>黄青野</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>孙思轩</t>
+          <t>孙星禾</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>林明远</t>
+          <t>林和野</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>李欣远</t>
+          <t>李墨野</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>郭梓杰</t>
+          <t>郭青辰</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>黄雨轩</t>
+          <t>黄南禾</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>郭浩涵</t>
+          <t>郭书秋</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>黄子轩</t>
+          <t>黄砚禾</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>马思远</t>
+          <t>马星野</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>朱明琪</t>
+          <t>朱和澜</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>赵浩怡</t>
+          <t>赵书言</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>王欣远</t>
+          <t>王墨野</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>高浩宇</t>
+          <t>高书白</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>朱子远</t>
+          <t>朱砚野</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>刘欣轩</t>
+          <t>刘墨禾</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>马梓琪</t>
+          <t>马青澜</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>周梓诺</t>
+          <t>周青桐</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>陈明桐</t>
+          <t>陈和乔</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>高思宇</t>
+          <t>高星白</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>胡一怡</t>
+          <t>胡疏言</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>林俊轩</t>
+          <t>林北舟</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>吴一诺</t>
+          <t>吴疏桐</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>何梓杰</t>
+          <t>何青辰</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>高明琪</t>
+          <t>高和澜</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>孙浩桐</t>
+          <t>孙书乔</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>周欣怡</t>
+          <t>周墨言</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>何佳琪</t>
+          <t>何听澜</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>何思琪</t>
+          <t>何星澜</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>胡思远</t>
+          <t>胡星野</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>郭思涵</t>
+          <t>郭星秋</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>朱一轩</t>
+          <t>朱疏禾</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>朱一涵</t>
+          <t>朱疏秋</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>林明杰</t>
+          <t>林和辰</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>胡浩杰</t>
+          <t>胡书辰</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>马俊轩</t>
+          <t>马北舟</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>孙明涵</t>
+          <t>孙和秋</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>李北辰</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>罗思远</t>
+          <t>罗星野</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>朱一杰</t>
+          <t>朱疏辰</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>徐思远</t>
+          <t>徐星野</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>朱梓宇</t>
+          <t>朱青白</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>林子轩</t>
+          <t>林砚禾</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>胡佳轩</t>
+          <t>胡听舟</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>朱浩远</t>
+          <t>朱书野</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>王浩远</t>
+          <t>王书野</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>徐明远</t>
+          <t>徐和野</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>郭雨涵</t>
+          <t>郭南秋</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>朱佳宇</t>
+          <t>朱听白</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>吴浩轩</t>
+          <t>吴书舟</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>吴明轩</t>
+          <t>吴和舟</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>刘明琪</t>
+          <t>刘和澜</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>何俊怡</t>
+          <t>何北言</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>朱雨怡</t>
+          <t>朱南言</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>张浩怡</t>
+          <t>张书言</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>马梓杰</t>
+          <t>马青辰</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>高明宇</t>
+          <t>高和白</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>赵思涵</t>
+          <t>赵星秋</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>马浩杰</t>
+          <t>马书辰</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>赵明杰</t>
+          <t>赵和辰</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>吴佳琪</t>
+          <t>吴听澜</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>林思琪</t>
+          <t>林星澜</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>李明宇</t>
+          <t>李和白</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>孙梓宇</t>
+          <t>孙青白</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>马思琪</t>
+          <t>马星澜</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>张子琪</t>
+          <t>张砚澜</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>马雨轩</t>
+          <t>马南禾</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>孙梓怡</t>
+          <t>孙青言</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>高佳怡</t>
+          <t>高听言</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>孙子怡</t>
+          <t>孙砚言</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>郭梓轩</t>
+          <t>郭青舟</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>王梓桐</t>
+          <t>王青乔</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>郭一远</t>
+          <t>郭疏野</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>杨欣远</t>
+          <t>杨墨野</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>杨俊远</t>
+          <t>杨北野</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>吴浩怡</t>
+          <t>吴书言</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>刘雨宇</t>
+          <t>刘南白</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>徐思远</t>
+          <t>徐星野</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>陈佳诺</t>
+          <t>陈听桐</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>张雨杰</t>
+          <t>张南辰</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>刘佳桐</t>
+          <t>刘听乔</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>马一轩</t>
+          <t>马疏禾</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>陈雨涵</t>
+          <t>陈南秋</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>郭一桐</t>
+          <t>郭疏乔</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>刘明轩</t>
+          <t>刘和禾</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>胡佳杰</t>
+          <t>胡听辰</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>吴雨杰</t>
+          <t>吴南辰</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
